--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2358,7 +2358,7 @@
         <v>129930299</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90631</v>
+        <v>90634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2358,7 +2358,7 @@
         <v>129930299</v>
       </c>
       <c r="B17" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90634</v>
+        <v>90637</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2358,7 +2358,7 @@
         <v>129930299</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90637</v>
+        <v>90638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2355,32 +2355,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129930299</v>
+        <v>129930291</v>
       </c>
       <c r="B17" t="n">
-        <v>78845</v>
+        <v>97692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715787</v>
+        <v>715773</v>
       </c>
       <c r="R17" t="n">
-        <v>7336317</v>
+        <v>7336148</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,32 +2461,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129930291</v>
+        <v>129930299</v>
       </c>
       <c r="B18" t="n">
-        <v>97675</v>
+        <v>78846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715773</v>
+        <v>715787</v>
       </c>
       <c r="R18" t="n">
-        <v>7336148</v>
+        <v>7336317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90638</v>
+        <v>90655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2358,7 +2358,7 @@
         <v>129930299</v>
       </c>
       <c r="B17" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90673</v>
+        <v>90760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -2358,7 +2358,7 @@
         <v>129930299</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>78852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129930291</v>
       </c>
       <c r="B18" t="n">
-        <v>97797</v>
+        <v>97710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>129930289</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>79714</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129930294</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>78852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>129930297</v>
       </c>
       <c r="B21" t="n">
-        <v>90760</v>
+        <v>90673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129930293</v>
       </c>
       <c r="B22" t="n">
-        <v>79799</v>
+        <v>79714</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>129930296</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>78761</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835031</v>
+        <v>91835033</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716108.9048081038</v>
+        <v>715924</v>
       </c>
       <c r="R2" t="n">
-        <v>7336114.851952379</v>
+        <v>7336061</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835029</v>
+        <v>129930296</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716108.9048081038</v>
+        <v>715609</v>
       </c>
       <c r="R3" t="n">
-        <v>7336114.851952379</v>
+        <v>7336215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91835038</v>
+        <v>91835022</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715674.9055668346</v>
+        <v>716113</v>
       </c>
       <c r="R4" t="n">
-        <v>7336151.003095832</v>
+        <v>7336114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +946,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835025</v>
+        <v>91835023</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715675.2145450284</v>
+        <v>715788</v>
       </c>
       <c r="R5" t="n">
-        <v>7336146.951406043</v>
+        <v>7336309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1043,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91835032</v>
+        <v>129930297</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1083,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715924.1010286002</v>
+        <v>715660</v>
       </c>
       <c r="R6" t="n">
-        <v>7336061.205474268</v>
+        <v>7336311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1141,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1166,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91835028</v>
+        <v>91835021</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1189,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715752.0313708263</v>
+        <v>715824</v>
       </c>
       <c r="R7" t="n">
-        <v>7336107.982169608</v>
+        <v>7336312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1246,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1275,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91835026</v>
+        <v>91835035</v>
       </c>
       <c r="B8" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716055.0344278701</v>
+        <v>715849</v>
       </c>
       <c r="R8" t="n">
-        <v>7336237.885754372</v>
+        <v>7336318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1343,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1372,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91835022</v>
+        <v>91835027</v>
       </c>
       <c r="B9" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716113.053929443</v>
+        <v>716033</v>
       </c>
       <c r="R9" t="n">
-        <v>7336113.946373276</v>
+        <v>7336251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1440,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1469,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91835023</v>
+        <v>91835026</v>
       </c>
       <c r="B10" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715788.0842774442</v>
+        <v>716055</v>
       </c>
       <c r="R10" t="n">
-        <v>7336309.194583556</v>
+        <v>7336238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1537,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1566,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91835033</v>
+        <v>91835024</v>
       </c>
       <c r="B11" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715924.1010286002</v>
+        <v>715924</v>
       </c>
       <c r="R11" t="n">
-        <v>7336061.205474268</v>
+        <v>7336061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1634,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1663,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91835037</v>
+        <v>91835019</v>
       </c>
       <c r="B12" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715803.0986651406</v>
+        <v>716109</v>
       </c>
       <c r="R12" t="n">
-        <v>7336320.935405339</v>
+        <v>7336115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1731,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91835021</v>
+        <v>91835038</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715824.1822563789</v>
+        <v>715675</v>
       </c>
       <c r="R13" t="n">
-        <v>7336311.949242709</v>
+        <v>7336151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1828,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91835019</v>
+        <v>129930294</v>
       </c>
       <c r="B14" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,17 +1885,21 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716108.9048081038</v>
+        <v>715632</v>
       </c>
       <c r="R14" t="n">
-        <v>7336114.851952379</v>
+        <v>7336199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,22 +1926,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,62 +1951,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91835024</v>
+        <v>129930299</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715924.1010286002</v>
+        <v>715787</v>
       </c>
       <c r="R15" t="n">
-        <v>7336061.205474268</v>
+        <v>7336317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,22 +2032,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,49 +2057,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91835027</v>
+        <v>91835031</v>
       </c>
       <c r="B16" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716032.8287214219</v>
+        <v>716109</v>
       </c>
       <c r="R16" t="n">
-        <v>7336250.860144077</v>
+        <v>7336115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2137,9 @@
           <t>2020-10-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-10-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129930299</v>
+        <v>91835032</v>
       </c>
       <c r="B17" t="n">
-        <v>78937</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,38 +2177,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715787</v>
+        <v>715924</v>
       </c>
       <c r="R17" t="n">
-        <v>7336317</v>
+        <v>7336061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,17 +2231,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,44 +2251,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129930291</v>
+        <v>129930289</v>
       </c>
       <c r="B18" t="n">
-        <v>97797</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2500,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715773</v>
+        <v>716104</v>
       </c>
       <c r="R18" t="n">
-        <v>7336148</v>
+        <v>7336105</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129930289</v>
+        <v>129930293</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,10 +2408,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716104</v>
+        <v>715633</v>
       </c>
       <c r="R19" t="n">
-        <v>7336105</v>
+        <v>7336200</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,32 +2475,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129930294</v>
+        <v>129930291</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>97989</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2712,10 +2514,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715632</v>
+        <v>715773</v>
       </c>
       <c r="R20" t="n">
-        <v>7336199</v>
+        <v>7336148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,10 +2581,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129930297</v>
+        <v>91835025</v>
       </c>
       <c r="B21" t="n">
-        <v>90760</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,38 +2592,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715660</v>
+        <v>715675</v>
       </c>
       <c r="R21" t="n">
-        <v>7336311</v>
+        <v>7336147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,17 +2646,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,22 +2666,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129930293</v>
+        <v>91835028</v>
       </c>
       <c r="B22" t="n">
-        <v>79799</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,38 +2689,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715633</v>
+        <v>715752</v>
       </c>
       <c r="R22" t="n">
-        <v>7336200</v>
+        <v>7336108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,17 +2743,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2979,22 +2763,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129930296</v>
+        <v>91835029</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,38 +2786,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715609</v>
+        <v>716109</v>
       </c>
       <c r="R23" t="n">
-        <v>7336215</v>
+        <v>7336115</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,17 +2840,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3085,15 +2860,218 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>91835037</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>715803</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7336321</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129930288</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>716068</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7336290</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60025-2025 artfynd.xlsx
+++ b/artfynd/A 60025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930297</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835021</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835027</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835024</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835038</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930294</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930299</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835031</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835032</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930289</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2472,6 +2562,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930293</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2578,6 +2673,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930291</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2675,6 +2775,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835028</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2869,6 +2979,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835029</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2966,6 +3081,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835037</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3072,8 +3192,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>